--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.03673469387755102</x:v>
+        <x:v>0.08163265306122448</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -558,12 +558,14 @@
       </x:c>
       <x:c r="H10" s="25" t="n">
         <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A10,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A10),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I10" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="J10" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="J10" s="24" t="str">
+        <x:v>Completed 2026-09-06: automated regression, coverage, frontend tests, and CI added.</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A11" s="24" t="str">
@@ -1345,14 +1347,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>9</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>236</x:v>
+        <x:v>225</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1361,7 +1363,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.03673469387755102</x:v>
+        <x:v>0.08163265306122448</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -1755,10 +1757,14 @@
       </x:c>
       <x:c r="I17" s="24" t="str"/>
       <x:c r="J17" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K17" s="24" t="str"/>
-      <x:c r="L17" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K17" s="24" t="str">
+        <x:v>Node test runner and guarded vms_test configuration added.</x:v>
+      </x:c>
+      <x:c r="L17" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A18" s="24" t="str">
@@ -1787,10 +1793,14 @@
       </x:c>
       <x:c r="I18" s="24" t="str"/>
       <x:c r="J18" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K18" s="24" t="str"/>
-      <x:c r="L18" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K18" s="24" t="str">
+        <x:v>Each backend run recreates vms_test and applies migrations 001-016.</x:v>
+      </x:c>
+      <x:c r="L18" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A19" s="24" t="str">
@@ -1819,10 +1829,14 @@
       </x:c>
       <x:c r="I19" s="24" t="str"/>
       <x:c r="J19" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K19" s="24" t="str"/>
-      <x:c r="L19" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K19" s="24" t="str">
+        <x:v>Current MVP and release regression scenarios are automated.</x:v>
+      </x:c>
+      <x:c r="L19" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A20" s="24" t="str">
@@ -1851,10 +1865,14 @@
       </x:c>
       <x:c r="I20" s="24" t="str"/>
       <x:c r="J20" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K20" s="24" t="str"/>
-      <x:c r="L20" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K20" s="24" t="str">
+        <x:v>Concurrent approval/billing duplicate protection is exercised.</x:v>
+      </x:c>
+      <x:c r="L20" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A21" s="24" t="str">
@@ -1883,10 +1901,14 @@
       </x:c>
       <x:c r="I21" s="24" t="str"/>
       <x:c r="J21" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K21" s="24" t="str"/>
-      <x:c r="L21" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K21" s="24" t="str">
+        <x:v>Vitest route-guard coverage added; further UI states evolve with modules.</x:v>
+      </x:c>
+      <x:c r="L21" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A22" s="24" t="str">
@@ -1915,10 +1937,14 @@
       </x:c>
       <x:c r="I22" s="24" t="str"/>
       <x:c r="J22" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K22" s="24" t="str"/>
-      <x:c r="L22" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K22" s="24" t="str">
+        <x:v>GitHub Actions runs MySQL-backed tests, lint, frontend tests, and build.</x:v>
+      </x:c>
+      <x:c r="L22" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A23" s="24" t="str">
@@ -1947,10 +1973,14 @@
       </x:c>
       <x:c r="I23" s="24" t="str"/>
       <x:c r="J23" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K23" s="24" t="str"/>
-      <x:c r="L23" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K23" s="24" t="str">
+        <x:v>c8 gate: 40% lines/functions, 30% branches for services/repositories.</x:v>
+      </x:c>
+      <x:c r="L23" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="24" t="str">
@@ -1979,10 +2009,14 @@
       </x:c>
       <x:c r="I24" s="24" t="str"/>
       <x:c r="J24" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K24" s="24" t="str"/>
-      <x:c r="L24" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K24" s="24" t="str">
+        <x:v>npm test starts its own local API and test database workflow.</x:v>
+      </x:c>
+      <x:c r="L24" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
       <x:c r="A25" s="24" t="str">
@@ -2011,10 +2045,14 @@
       </x:c>
       <x:c r="I25" s="24" t="str"/>
       <x:c r="J25" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K25" s="24" t="str"/>
-      <x:c r="L25" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K25" s="24" t="str">
+        <x:v>CI provisions isolated MySQL 8 service.</x:v>
+      </x:c>
+      <x:c r="L25" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
       <x:c r="A26" s="24" t="str">
@@ -2043,10 +2081,14 @@
       </x:c>
       <x:c r="I26" s="24" t="str"/>
       <x:c r="J26" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K26" s="24" t="str"/>
-      <x:c r="L26" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K26" s="24" t="str">
+        <x:v>Known milestone billing regression passes in automated suite.</x:v>
+      </x:c>
+      <x:c r="L26" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
       <x:c r="A27" s="24" t="str">
@@ -2075,10 +2117,14 @@
       </x:c>
       <x:c r="I27" s="24" t="str"/>
       <x:c r="J27" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K27" s="24" t="str"/>
-      <x:c r="L27" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K27" s="24" t="str">
+        <x:v>Concurrent milestone approvals assert no duplicate billing contributions.</x:v>
+      </x:c>
+      <x:c r="L27" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A28" s="24" t="str">

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -564,7 +564,7 @@
         <x:v>☑</x:v>
       </x:c>
       <x:c r="J10" s="24" t="str">
-        <x:v>Completed 2026-09-06: automated regression, coverage, frontend tests, and CI added.</x:v>
+        <x:v>Completed 2026-09-06: automated regression, coverage, frontend tests, and CI added; owner verified green push and pull-request runs.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="26.399999618530273" hidden="0" customHeight="1">

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rac9fb4be024b4d94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R555afa77687d418f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R9471c1491a44403a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="Rfc74ff4883bc4764"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="Re8b06af06a60478f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rc359067abc2540d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R28369c959cb942de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="Rd7e2ac10c8df470a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="Re877a763c0ba489b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="Ra13f5f62153245dd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -151,7 +151,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDFF2E3"/>
         </x:patternFill>
       </x:fill>
@@ -162,7 +162,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDFF2E3"/>
         </x:patternFill>
       </x:fill>
@@ -173,7 +173,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDECEC"/>
         </x:patternFill>
       </x:fill>
@@ -184,7 +184,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF3CD"/>
         </x:patternFill>
       </x:fill>
@@ -195,7 +195,7 @@
         <x:color rgb="FF1F4E79"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF3F6"/>
         </x:patternFill>
       </x:fill>
@@ -206,7 +206,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDFF2E3"/>
         </x:patternFill>
       </x:fill>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.08163265306122448</x:v>
+        <x:v>0.12601626016260162</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -590,13 +590,14 @@
         <x:v>Replace hackathon-grade authentication with a production-shaped session and account-recovery design.</x:v>
       </x:c>
       <x:c r="H11" s="25" t="n">
-        <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A11,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A11),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I11" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="J11" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="J11" s="24" t="str">
+        <x:v>Completed 2026-09-06: session-bound access tokens, rotating refresh cookies, recovery, invitations, security controls, automated tests, and manual flow verification.</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A12" s="24" t="str">
@@ -1347,14 +1348,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>20</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>225</x:v>
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1363,7 +1364,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.08163265306122448</x:v>
+        <x:v>0.12653061224489795</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -2153,10 +2154,14 @@
       </x:c>
       <x:c r="I28" s="24" t="str"/>
       <x:c r="J28" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K28" s="24" t="str"/>
-      <x:c r="L28" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K28" s="24" t="str">
+        <x:v>Helmet, CORS allowlist, body limit, auth limiter and progressive lockout verified.</x:v>
+      </x:c>
+      <x:c r="L28" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A29" s="24" t="str">
@@ -2185,10 +2190,14 @@
       </x:c>
       <x:c r="I29" s="24" t="str"/>
       <x:c r="J29" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K29" s="24" t="str"/>
-      <x:c r="L29" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K29" s="24" t="str">
+        <x:v>Short access JWTs are session-bound; rotating HttpOnly refresh cookie supports revocation/logout-all.</x:v>
+      </x:c>
+      <x:c r="L29" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A30" s="24" t="str">
@@ -2217,10 +2226,14 @@
       </x:c>
       <x:c r="I30" s="24" t="str"/>
       <x:c r="J30" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K30" s="24" t="str"/>
-      <x:c r="L30" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K30" s="24" t="str">
+        <x:v>Generic, hashed, expiring, single-use reset tokens verified.</x:v>
+      </x:c>
+      <x:c r="L30" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A31" s="24" t="str">
@@ -2249,10 +2262,14 @@
       </x:c>
       <x:c r="I31" s="24" t="str"/>
       <x:c r="J31" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K31" s="24" t="str"/>
-      <x:c r="L31" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K31" s="24" t="str">
+        <x:v>Vendor creates identity; contractor sets password using replaceable one-time invitation.</x:v>
+      </x:c>
+      <x:c r="L31" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A32" s="24" t="str">
@@ -2281,10 +2298,14 @@
       </x:c>
       <x:c r="I32" s="24" t="str"/>
       <x:c r="J32" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K32" s="24" t="str"/>
-      <x:c r="L32" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K32" s="24" t="str">
+        <x:v>Auth fields rejected, emails normalized, login/recovery remain generic.</x:v>
+      </x:c>
+      <x:c r="L32" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="33" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A33" s="24" t="str">
@@ -2313,10 +2334,14 @@
       </x:c>
       <x:c r="I33" s="24" t="str"/>
       <x:c r="J33" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K33" s="24" t="str"/>
-      <x:c r="L33" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K33" s="24" t="str">
+        <x:v>Memory-only access token, cookie restoration, reset/setup screens, logout-all UI added.</x:v>
+      </x:c>
+      <x:c r="L33" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="34" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A34" s="24" t="str">
@@ -2345,10 +2370,14 @@
       </x:c>
       <x:c r="I34" s="24" t="str"/>
       <x:c r="J34" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K34" s="24" t="str"/>
-      <x:c r="L34" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K34" s="24" t="str">
+        <x:v>Integration coverage includes lockout, rotation, revocation, reset/invite expiry and replay.</x:v>
+      </x:c>
+      <x:c r="L34" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="35" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A35" s="24" t="str">
@@ -2377,10 +2406,14 @@
       </x:c>
       <x:c r="I35" s="24" t="str"/>
       <x:c r="J35" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K35" s="24" t="str"/>
-      <x:c r="L35" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K35" s="24" t="str">
+        <x:v>Repeated failures are rate-limited and locked after configured threshold.</x:v>
+      </x:c>
+      <x:c r="L35" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="36" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A36" s="24" t="str">
@@ -2409,10 +2442,14 @@
       </x:c>
       <x:c r="I36" s="24" t="str"/>
       <x:c r="J36" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K36" s="24" t="str"/>
-      <x:c r="L36" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K36" s="24" t="str">
+        <x:v>Session-bound access JWT is rejected immediately after revocation.</x:v>
+      </x:c>
+      <x:c r="L36" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="37" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A37" s="24" t="str">
@@ -2441,10 +2478,14 @@
       </x:c>
       <x:c r="I37" s="24" t="str"/>
       <x:c r="J37" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K37" s="24" t="str"/>
-      <x:c r="L37" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K37" s="24" t="str">
+        <x:v>Known and unknown recovery requests return the same accepted response.</x:v>
+      </x:c>
+      <x:c r="L37" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="38" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A38" s="24" t="str">
@@ -2473,10 +2514,14 @@
       </x:c>
       <x:c r="I38" s="24" t="str"/>
       <x:c r="J38" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K38" s="24" t="str"/>
-      <x:c r="L38" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K38" s="24" t="str">
+        <x:v>Contractor receives invitation and chooses the only usable password.</x:v>
+      </x:c>
+      <x:c r="L38" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="39" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A39" s="24" t="str">

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rc359067abc2540d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R28369c959cb942de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="Rd7e2ac10c8df470a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="Re877a763c0ba489b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="Ra13f5f62153245dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rf43e9d8b91664b18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Rf022cc1128dc46f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R7b5a349ffea94c84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R402578cd02904479"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R1954ff895cfe420c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.12601626016260162</x:v>
+        <x:v>0.16260162601626016</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -622,13 +622,14 @@
         <x:v>Make failures diagnosable without exposing internals to users.</x:v>
       </x:c>
       <x:c r="H12" s="25" t="n">
-        <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A12,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A12),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I12" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="J12" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="J12" s="24" t="str">
+        <x:v>Completed 2026-09-06: structured redacted logging, request-correlated error contracts, health semantics, metrics, tests, and documentation.</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="24" t="str">
@@ -1348,14 +1349,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>31</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>214</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1364,7 +1365,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.12653061224489795</x:v>
+        <x:v>0.16326530612244897</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -2550,10 +2551,14 @@
       </x:c>
       <x:c r="I39" s="24" t="str"/>
       <x:c r="J39" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K39" s="24" t="str"/>
-      <x:c r="L39" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K39" s="24" t="str">
+        <x:v>Redacted JSON request logs include route, actor, status, latency, and request ID.</x:v>
+      </x:c>
+      <x:c r="L39" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="40" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A40" s="24" t="str">
@@ -2582,10 +2587,14 @@
       </x:c>
       <x:c r="I40" s="24" t="str"/>
       <x:c r="J40" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K40" s="24" t="str"/>
-      <x:c r="L40" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K40" s="24" t="str">
+        <x:v>Safe inbound IDs are accepted/generated and returned in headers and errors.</x:v>
+      </x:c>
+      <x:c r="L40" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A41" s="24" t="str">
@@ -2614,10 +2623,14 @@
       </x:c>
       <x:c r="I41" s="24" t="str"/>
       <x:c r="J41" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K41" s="24" t="str"/>
-      <x:c r="L41" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K41" s="24" t="str">
+        <x:v>Stable API/domain codes and DB constraint mapping are implemented.</x:v>
+      </x:c>
+      <x:c r="L41" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="42" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A42" s="24" t="str">
@@ -2646,10 +2659,14 @@
       </x:c>
       <x:c r="I42" s="24" t="str"/>
       <x:c r="J42" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K42" s="24" t="str"/>
-      <x:c r="L42" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K42" s="24" t="str">
+        <x:v>Liveness and DB readiness routes expose safe dependency state.</x:v>
+      </x:c>
+      <x:c r="L42" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A43" s="24" t="str">
@@ -2678,10 +2695,14 @@
       </x:c>
       <x:c r="I43" s="24" t="str"/>
       <x:c r="J43" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K43" s="24" t="str"/>
-      <x:c r="L43" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K43" s="24" t="str">
+        <x:v>In-process counts and latency cover the required operational event categories.</x:v>
+      </x:c>
+      <x:c r="L43" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A44" s="24" t="str">
@@ -2710,10 +2731,14 @@
       </x:c>
       <x:c r="I44" s="24" t="str"/>
       <x:c r="J44" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K44" s="24" t="str"/>
-      <x:c r="L44" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K44" s="24" t="str">
+        <x:v>Integration coverage verifies IDs, contracts, redaction, health, and metrics.</x:v>
+      </x:c>
+      <x:c r="L44" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="45" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A45" s="24" t="str">
@@ -2742,10 +2767,14 @@
       </x:c>
       <x:c r="I45" s="24" t="str"/>
       <x:c r="J45" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K45" s="24" t="str"/>
-      <x:c r="L45" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K45" s="24" t="str">
+        <x:v>Each production error response is correlated with a request ID.</x:v>
+      </x:c>
+      <x:c r="L45" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A46" s="24" t="str">
@@ -2774,10 +2803,14 @@
       </x:c>
       <x:c r="I46" s="24" t="str"/>
       <x:c r="J46" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K46" s="24" t="str"/>
-      <x:c r="L46" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K46" s="24" t="str">
+        <x:v>Client contracts expose stable codes, messages, optional details, and request ID.</x:v>
+      </x:c>
+      <x:c r="L46" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A47" s="24" t="str">
@@ -2806,10 +2839,14 @@
       </x:c>
       <x:c r="I47" s="24" t="str"/>
       <x:c r="J47" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K47" s="24" t="str"/>
-      <x:c r="L47" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K47" s="24" t="str">
+        <x:v>Logger recursively redacts sensitive structured fields and error diagnostics.</x:v>
+      </x:c>
+      <x:c r="L47" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A48" s="24" t="str">

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rf43e9d8b91664b18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Rf022cc1128dc46f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R7b5a349ffea94c84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R402578cd02904479"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R1954ff895cfe420c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rb097d6580f76491d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R36bfabbda8d444dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R1b99a165ea034ba1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R2bd3ef46caf54f05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="Rfce809b2fbe84435"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.16260162601626016</x:v>
+        <x:v>0.1991869918699187</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -654,13 +654,14 @@
         <x:v>Create a real who-did-what-when trail for business-critical state changes.</x:v>
       </x:c>
       <x:c r="H13" s="25" t="n">
-        <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A13,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A13),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I13" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="J13" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="J13" s="24" t="str">
+        <x:v>Completed 2026-09-06: transactional append-only audit logging, current critical-mutation coverage, rollback/redaction tests, and verification completed.</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A14" s="24" t="str">
@@ -1349,14 +1350,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>40</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>205</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1365,7 +1366,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.16326530612244897</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -2875,7 +2876,7 @@
       </x:c>
       <x:c r="I48" s="24" t="str"/>
       <x:c r="J48" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K48" s="24" t="str"/>
       <x:c r="L48" s="24"/>
@@ -2907,7 +2908,7 @@
       </x:c>
       <x:c r="I49" s="24" t="str"/>
       <x:c r="J49" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K49" s="24" t="str"/>
       <x:c r="L49" s="24"/>
@@ -2939,7 +2940,7 @@
       </x:c>
       <x:c r="I50" s="24" t="str"/>
       <x:c r="J50" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K50" s="24" t="str"/>
       <x:c r="L50" s="24"/>
@@ -2971,7 +2972,7 @@
       </x:c>
       <x:c r="I51" s="24" t="str"/>
       <x:c r="J51" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K51" s="24" t="str"/>
       <x:c r="L51" s="24"/>
@@ -3003,7 +3004,7 @@
       </x:c>
       <x:c r="I52" s="24" t="str"/>
       <x:c r="J52" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K52" s="24" t="str"/>
       <x:c r="L52" s="24"/>
@@ -3035,7 +3036,7 @@
       </x:c>
       <x:c r="I53" s="24" t="str"/>
       <x:c r="J53" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K53" s="24" t="str"/>
       <x:c r="L53" s="24"/>
@@ -3067,7 +3068,7 @@
       </x:c>
       <x:c r="I54" s="24" t="str"/>
       <x:c r="J54" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K54" s="24" t="str"/>
       <x:c r="L54" s="24"/>
@@ -3099,7 +3100,7 @@
       </x:c>
       <x:c r="I55" s="24" t="str"/>
       <x:c r="J55" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K55" s="24" t="str"/>
       <x:c r="L55" s="24"/>
@@ -3131,7 +3132,7 @@
       </x:c>
       <x:c r="I56" s="24" t="str"/>
       <x:c r="J56" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K56" s="24" t="str"/>
       <x:c r="L56" s="24"/>

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rb097d6580f76491d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R36bfabbda8d444dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R1b99a165ea034ba1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R2bd3ef46caf54f05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="Rfce809b2fbe84435"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="R5469c70628c54dd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R0ec3c49b33034e4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R575729d453fc4449"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="Rc3499d48b9f94a8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="Rb4ae49da4b134efa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.1991869918699187</x:v>
+        <x:v>0.23983739837398374</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -686,13 +686,14 @@
         <x:v>Make list endpoints scale beyond demo data and make the API contract explicit.</x:v>
       </x:c>
       <x:c r="H14" s="25" t="n">
-        <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A14,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A14),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I14" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="J14" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="J14" s="24" t="str">
+        <x:v>Completed 2026-09-06: paginated SQL list APIs, indexes, frontend controls, OpenAPI, tests, and audit verified.</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A15" s="24" t="str">
@@ -1350,14 +1351,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>196</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1366,7 +1367,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.2</x:v>
+        <x:v>0.24081632653061225</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -3164,7 +3165,7 @@
       </x:c>
       <x:c r="I57" s="24" t="str"/>
       <x:c r="J57" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K57" s="24" t="str"/>
       <x:c r="L57" s="24"/>
@@ -3196,7 +3197,7 @@
       </x:c>
       <x:c r="I58" s="24" t="str"/>
       <x:c r="J58" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K58" s="24" t="str"/>
       <x:c r="L58" s="24"/>
@@ -3228,7 +3229,7 @@
       </x:c>
       <x:c r="I59" s="24" t="str"/>
       <x:c r="J59" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K59" s="24" t="str"/>
       <x:c r="L59" s="24"/>
@@ -3260,7 +3261,7 @@
       </x:c>
       <x:c r="I60" s="24" t="str"/>
       <x:c r="J60" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K60" s="24" t="str"/>
       <x:c r="L60" s="24"/>
@@ -3292,7 +3293,7 @@
       </x:c>
       <x:c r="I61" s="24" t="str"/>
       <x:c r="J61" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K61" s="24" t="str"/>
       <x:c r="L61" s="24"/>
@@ -3324,7 +3325,7 @@
       </x:c>
       <x:c r="I62" s="24" t="str"/>
       <x:c r="J62" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K62" s="24" t="str"/>
       <x:c r="L62" s="24"/>
@@ -3356,7 +3357,7 @@
       </x:c>
       <x:c r="I63" s="24" t="str"/>
       <x:c r="J63" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K63" s="24" t="str"/>
       <x:c r="L63" s="24"/>
@@ -3388,10 +3389,12 @@
       </x:c>
       <x:c r="I64" s="24" t="str"/>
       <x:c r="J64" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K64" s="24" t="str"/>
-      <x:c r="L64" s="24"/>
+      <x:c r="L64" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="65" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A65" s="24" t="str">
@@ -3420,10 +3423,12 @@
       </x:c>
       <x:c r="I65" s="24" t="str"/>
       <x:c r="J65" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K65" s="24" t="str"/>
-      <x:c r="L65" s="24"/>
+      <x:c r="L65" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="66" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A66" s="24" t="str">
@@ -3452,10 +3457,12 @@
       </x:c>
       <x:c r="I66" s="24" t="str"/>
       <x:c r="J66" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K66" s="24" t="str"/>
-      <x:c r="L66" s="24"/>
+      <x:c r="L66" s="24" t="str">
+        <x:v>2026-09-06</x:v>
+      </x:c>
     </x:row>
     <x:row r="67" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A67" s="24" t="str">

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="R5469c70628c54dd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R0ec3c49b33034e4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R575729d453fc4449"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="Rc3499d48b9f94a8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="Rb4ae49da4b134efa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rf5f89d5c0b524967"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Rd32dc1ab93024191"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R438ae1e0ebdb4105"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="Rab4ee93af44d4c91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R9c95f6091f0740b5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.23983739837398374</x:v>
+        <x:v>0.2886178861788618</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -719,12 +719,14 @@
       </x:c>
       <x:c r="H15" s="25" t="n">
         <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A15,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A15),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I15" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="J15" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="J15" s="24" t="str">
+        <x:v>Completed 2026-09-07: draft/submission, reasoned review, bulk review, tests, audit, OpenAPI, and M06 documentation verified.</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A16" s="24" t="str">
@@ -1351,14 +1353,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>59</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>186</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1367,7 +1369,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.24081632653061225</x:v>
+        <x:v>0.2897959183673469</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -3491,7 +3493,7 @@
       </x:c>
       <x:c r="I67" s="24" t="str"/>
       <x:c r="J67" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K67" s="24" t="str"/>
       <x:c r="L67" s="24"/>
@@ -3523,7 +3525,7 @@
       </x:c>
       <x:c r="I68" s="24" t="str"/>
       <x:c r="J68" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K68" s="24" t="str"/>
       <x:c r="L68" s="24"/>
@@ -3555,7 +3557,7 @@
       </x:c>
       <x:c r="I69" s="24" t="str"/>
       <x:c r="J69" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K69" s="24" t="str"/>
       <x:c r="L69" s="24"/>
@@ -3587,7 +3589,7 @@
       </x:c>
       <x:c r="I70" s="24" t="str"/>
       <x:c r="J70" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K70" s="24" t="str"/>
       <x:c r="L70" s="24"/>
@@ -3619,7 +3621,7 @@
       </x:c>
       <x:c r="I71" s="24" t="str"/>
       <x:c r="J71" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K71" s="24" t="str"/>
       <x:c r="L71" s="24"/>
@@ -3651,7 +3653,7 @@
       </x:c>
       <x:c r="I72" s="24" t="str"/>
       <x:c r="J72" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K72" s="24" t="str"/>
       <x:c r="L72" s="24"/>
@@ -3683,7 +3685,7 @@
       </x:c>
       <x:c r="I73" s="24" t="str"/>
       <x:c r="J73" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K73" s="24" t="str"/>
       <x:c r="L73" s="24"/>
@@ -3715,7 +3717,7 @@
       </x:c>
       <x:c r="I74" s="24" t="str"/>
       <x:c r="J74" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K74" s="24" t="str"/>
       <x:c r="L74" s="24"/>
@@ -3747,7 +3749,7 @@
       </x:c>
       <x:c r="I75" s="24" t="str"/>
       <x:c r="J75" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K75" s="24" t="str"/>
       <x:c r="L75" s="24"/>
@@ -3779,7 +3781,7 @@
       </x:c>
       <x:c r="I76" s="24" t="str"/>
       <x:c r="J76" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K76" s="24" t="str"/>
       <x:c r="L76" s="24"/>
@@ -3811,7 +3813,7 @@
       </x:c>
       <x:c r="I77" s="24" t="str"/>
       <x:c r="J77" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K77" s="24" t="str"/>
       <x:c r="L77" s="24"/>
@@ -3843,7 +3845,7 @@
       </x:c>
       <x:c r="I78" s="24" t="str"/>
       <x:c r="J78" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K78" s="24" t="str"/>
       <x:c r="L78" s="24"/>

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rf5f89d5c0b524967"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Rd32dc1ab93024191"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R438ae1e0ebdb4105"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="Rab4ee93af44d4c91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R9c95f6091f0740b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rabe98cecde4c4bb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Rcbe9f5b17a32435f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R4899f5debd8c44c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="Rc52e98f2de904c92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R81ac61f14aae40bf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.2886178861788618</x:v>
+        <x:v>0.32926829268292684</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -752,10 +752,10 @@
       </x:c>
       <x:c r="H16" s="25" t="n">
         <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A16,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A16),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="J16" s="24" t="str"/>
     </x:row>
@@ -1353,14 +1353,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>71</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>174</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1369,7 +1369,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.2897959183673469</x:v>
+        <x:v>0.3306122448979592</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -3877,7 +3877,7 @@
       </x:c>
       <x:c r="I79" s="24" t="str"/>
       <x:c r="J79" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K79" s="24" t="str"/>
       <x:c r="L79" s="24"/>
@@ -3909,7 +3909,7 @@
       </x:c>
       <x:c r="I80" s="24" t="str"/>
       <x:c r="J80" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K80" s="24" t="str"/>
       <x:c r="L80" s="24"/>
@@ -3941,7 +3941,7 @@
       </x:c>
       <x:c r="I81" s="24" t="str"/>
       <x:c r="J81" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K81" s="24" t="str"/>
       <x:c r="L81" s="24"/>
@@ -3973,7 +3973,7 @@
       </x:c>
       <x:c r="I82" s="24" t="str"/>
       <x:c r="J82" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K82" s="24" t="str"/>
       <x:c r="L82" s="24"/>
@@ -4005,7 +4005,7 @@
       </x:c>
       <x:c r="I83" s="24" t="str"/>
       <x:c r="J83" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K83" s="24" t="str"/>
       <x:c r="L83" s="24"/>
@@ -4037,7 +4037,7 @@
       </x:c>
       <x:c r="I84" s="24" t="str"/>
       <x:c r="J84" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K84" s="24" t="str"/>
       <x:c r="L84" s="24"/>
@@ -4069,7 +4069,7 @@
       </x:c>
       <x:c r="I85" s="24" t="str"/>
       <x:c r="J85" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K85" s="24" t="str"/>
       <x:c r="L85" s="24"/>
@@ -4101,7 +4101,7 @@
       </x:c>
       <x:c r="I86" s="24" t="str"/>
       <x:c r="J86" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K86" s="24" t="str"/>
       <x:c r="L86" s="24"/>
@@ -4133,7 +4133,7 @@
       </x:c>
       <x:c r="I87" s="24" t="str"/>
       <x:c r="J87" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K87" s="24" t="str"/>
       <x:c r="L87" s="24"/>
@@ -4165,7 +4165,7 @@
       </x:c>
       <x:c r="I88" s="24" t="str"/>
       <x:c r="J88" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K88" s="24" t="str"/>
       <x:c r="L88" s="24"/>

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rabe98cecde4c4bb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Rcbe9f5b17a32435f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R4899f5debd8c44c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="Rc52e98f2de904c92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R81ac61f14aae40bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Redc7543624bf4265"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R61e3c189cf474e77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="Rd53d721b096d4c81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="Rae3848927a0b4cc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R0207ea479fab471f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.32926829268292684</x:v>
+        <x:v>0.37398373983739835</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -783,10 +783,10 @@
       </x:c>
       <x:c r="H17" s="25" t="n">
         <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A17,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A17),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I17" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="J17" s="24" t="str"/>
     </x:row>
@@ -1353,14 +1353,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>81</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>164</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1369,7 +1369,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.3306122448979592</x:v>
+        <x:v>0.37551020408163266</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -4197,7 +4197,7 @@
       </x:c>
       <x:c r="I89" s="24" t="str"/>
       <x:c r="J89" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K89" s="24" t="str"/>
       <x:c r="L89" s="24"/>
@@ -4229,7 +4229,7 @@
       </x:c>
       <x:c r="I90" s="24" t="str"/>
       <x:c r="J90" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K90" s="24" t="str"/>
       <x:c r="L90" s="24"/>
@@ -4261,7 +4261,7 @@
       </x:c>
       <x:c r="I91" s="24" t="str"/>
       <x:c r="J91" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K91" s="24" t="str"/>
       <x:c r="L91" s="24"/>
@@ -4293,7 +4293,7 @@
       </x:c>
       <x:c r="I92" s="24" t="str"/>
       <x:c r="J92" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K92" s="24" t="str"/>
       <x:c r="L92" s="24"/>
@@ -4325,7 +4325,7 @@
       </x:c>
       <x:c r="I93" s="24" t="str"/>
       <x:c r="J93" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K93" s="24" t="str"/>
       <x:c r="L93" s="24"/>
@@ -4357,7 +4357,7 @@
       </x:c>
       <x:c r="I94" s="24" t="str"/>
       <x:c r="J94" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K94" s="24" t="str"/>
       <x:c r="L94" s="24"/>
@@ -4389,7 +4389,7 @@
       </x:c>
       <x:c r="I95" s="24" t="str"/>
       <x:c r="J95" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K95" s="24" t="str"/>
       <x:c r="L95" s="24"/>
@@ -4421,7 +4421,7 @@
       </x:c>
       <x:c r="I96" s="24" t="str"/>
       <x:c r="J96" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K96" s="24" t="str"/>
       <x:c r="L96" s="24"/>
@@ -4453,7 +4453,7 @@
       </x:c>
       <x:c r="I97" s="24" t="str"/>
       <x:c r="J97" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K97" s="24" t="str"/>
       <x:c r="L97" s="24"/>
@@ -4485,7 +4485,7 @@
       </x:c>
       <x:c r="I98" s="24" t="str"/>
       <x:c r="J98" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K98" s="24" t="str"/>
       <x:c r="L98" s="24"/>
@@ -4517,7 +4517,7 @@
       </x:c>
       <x:c r="I99" s="24" t="str"/>
       <x:c r="J99" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K99" s="24" t="str"/>
       <x:c r="L99" s="24"/>

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Redc7543624bf4265"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R61e3c189cf474e77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="Rd53d721b096d4c81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="Rae3848927a0b4cc0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R0207ea479fab471f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rfd7b76fc2ac1483e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R714024923037499e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R24aa68ad6fc9499d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R9aeb08b4fd3342ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R4c21bdbc0b4f4aa0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.37398373983739835</x:v>
+        <x:v>0.4186991869918699</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -814,12 +814,14 @@
       </x:c>
       <x:c r="H18" s="25" t="n">
         <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A18,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A18),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I18" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="J18" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="J18" s="24" t="str">
+        <x:v>Completed 2026-09-07: invitation-only existing-company membership, scoped Vendor relationships/project access, Vendor client directory/detail, audited revocation, and full regression verification.</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A19" s="24" t="str">
@@ -845,7 +847,7 @@
       </x:c>
       <x:c r="H19" s="25" t="n">
         <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A19,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A19),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.09090909090909091</x:v>
       </x:c>
       <x:c r="I19" s="24" t="str">
         <x:v>☐</x:v>
@@ -1353,14 +1355,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>92</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>153</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1369,7 +1371,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.37551020408163266</x:v>
+        <x:v>0.4204081632653061</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -4549,7 +4551,7 @@
       </x:c>
       <x:c r="I100" s="24" t="str"/>
       <x:c r="J100" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K100" s="24" t="str"/>
       <x:c r="L100" s="24"/>
@@ -4581,7 +4583,7 @@
       </x:c>
       <x:c r="I101" s="24" t="str"/>
       <x:c r="J101" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K101" s="24" t="str"/>
       <x:c r="L101" s="24"/>
@@ -4613,7 +4615,7 @@
       </x:c>
       <x:c r="I102" s="24" t="str"/>
       <x:c r="J102" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K102" s="24" t="str"/>
       <x:c r="L102" s="24"/>
@@ -4645,7 +4647,7 @@
       </x:c>
       <x:c r="I103" s="24" t="str"/>
       <x:c r="J103" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K103" s="24" t="str"/>
       <x:c r="L103" s="24"/>
@@ -4677,7 +4679,7 @@
       </x:c>
       <x:c r="I104" s="24" t="str"/>
       <x:c r="J104" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K104" s="24" t="str"/>
       <x:c r="L104" s="24"/>
@@ -4709,7 +4711,7 @@
       </x:c>
       <x:c r="I105" s="24" t="str"/>
       <x:c r="J105" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K105" s="24" t="str"/>
       <x:c r="L105" s="24"/>
@@ -4741,7 +4743,7 @@
       </x:c>
       <x:c r="I106" s="24" t="str"/>
       <x:c r="J106" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K106" s="24" t="str"/>
       <x:c r="L106" s="24"/>
@@ -4773,7 +4775,7 @@
       </x:c>
       <x:c r="I107" s="24" t="str"/>
       <x:c r="J107" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K107" s="24" t="str"/>
       <x:c r="L107" s="24"/>
@@ -4805,7 +4807,7 @@
       </x:c>
       <x:c r="I108" s="24" t="str"/>
       <x:c r="J108" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K108" s="24" t="str"/>
       <x:c r="L108" s="24"/>
@@ -4837,7 +4839,7 @@
       </x:c>
       <x:c r="I109" s="24" t="str"/>
       <x:c r="J109" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K109" s="24" t="str"/>
       <x:c r="L109" s="24"/>
@@ -4869,7 +4871,7 @@
       </x:c>
       <x:c r="I110" s="24" t="str"/>
       <x:c r="J110" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K110" s="24" t="str"/>
       <x:c r="L110" s="24"/>

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rfd7b76fc2ac1483e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R714024923037499e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R24aa68ad6fc9499d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R9aeb08b4fd3342ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R4c21bdbc0b4f4aa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="R6babdf20209f4629"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Rc0470e9baaeb46a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R2a7ce4a4af4541ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="Rad675244829a47f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="Rb227a1901f594693"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.4186991869918699</x:v>
+        <x:v>0.45934959349593496</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -847,7 +847,7 @@
       </x:c>
       <x:c r="H19" s="25" t="n">
         <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A19,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A19),0)</x:f>
-        <x:v>0.09090909090909091</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="24" t="str">
         <x:v>☐</x:v>
@@ -1355,14 +1355,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>103</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>142</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1371,7 +1371,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.4204081632653061</x:v>
+        <x:v>0.46122448979591835</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -4903,7 +4903,7 @@
       </x:c>
       <x:c r="I111" s="24" t="str"/>
       <x:c r="J111" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K111" s="24" t="str"/>
       <x:c r="L111" s="24"/>
@@ -4935,7 +4935,7 @@
       </x:c>
       <x:c r="I112" s="24" t="str"/>
       <x:c r="J112" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K112" s="24" t="str"/>
       <x:c r="L112" s="24"/>
@@ -4967,7 +4967,7 @@
       </x:c>
       <x:c r="I113" s="24" t="str"/>
       <x:c r="J113" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K113" s="24" t="str"/>
       <x:c r="L113" s="24"/>
@@ -4999,7 +4999,7 @@
       </x:c>
       <x:c r="I114" s="24" t="str"/>
       <x:c r="J114" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K114" s="24" t="str"/>
       <x:c r="L114" s="24"/>
@@ -5031,7 +5031,7 @@
       </x:c>
       <x:c r="I115" s="24" t="str"/>
       <x:c r="J115" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K115" s="24" t="str"/>
       <x:c r="L115" s="24"/>
@@ -5063,7 +5063,7 @@
       </x:c>
       <x:c r="I116" s="24" t="str"/>
       <x:c r="J116" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K116" s="24" t="str"/>
       <x:c r="L116" s="24"/>
@@ -5095,7 +5095,7 @@
       </x:c>
       <x:c r="I117" s="24" t="str"/>
       <x:c r="J117" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K117" s="24" t="str"/>
       <x:c r="L117" s="24"/>
@@ -5127,7 +5127,7 @@
       </x:c>
       <x:c r="I118" s="24" t="str"/>
       <x:c r="J118" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K118" s="24" t="str"/>
       <x:c r="L118" s="24"/>
@@ -5159,7 +5159,7 @@
       </x:c>
       <x:c r="I119" s="24" t="str"/>
       <x:c r="J119" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K119" s="24" t="str"/>
       <x:c r="L119" s="24"/>
@@ -5191,7 +5191,7 @@
       </x:c>
       <x:c r="I120" s="24" t="str"/>
       <x:c r="J120" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K120" s="24" t="str"/>
       <x:c r="L120" s="24"/>

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="R6babdf20209f4629"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Rc0470e9baaeb46a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R2a7ce4a4af4541ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="Rad675244829a47f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="Rb227a1901f594693"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rda264549d40d44ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R5db31af403954d1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="Rcbea06f832c34923"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R0a5b932c22ee4d1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R002746b1e24c4a04"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.45934959349593496</x:v>
+        <x:v>0.5040650406504065</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -877,13 +877,14 @@
         <x:v>Replace the global one-ACTIVE-assignment rule with date-aware availability and controlled individual release.</x:v>
       </x:c>
       <x:c r="H20" s="25" t="n">
-        <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A20,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A20),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="J20" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="J20" s="24" t="str">
+        <x:v>Completed 2026-09-07: date-aware assignment scheduling, vendor/contractor availability, controlled release, UI, audit, migration, concurrency tests, and full regression verification.</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A21" s="24" t="str">
@@ -909,7 +910,7 @@
       </x:c>
       <x:c r="H21" s="25" t="n">
         <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A21,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A21),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.09090909090909091</x:v>
       </x:c>
       <x:c r="I21" s="24" t="str">
         <x:v>☐</x:v>
@@ -1355,14 +1356,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>113</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>132</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1371,7 +1372,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.46122448979591835</x:v>
+        <x:v>0.5061224489795918</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -5255,7 +5256,7 @@
       </x:c>
       <x:c r="I122" s="24" t="str"/>
       <x:c r="J122" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K122" s="24" t="str"/>
       <x:c r="L122" s="24"/>
@@ -5287,7 +5288,7 @@
       </x:c>
       <x:c r="I123" s="24" t="str"/>
       <x:c r="J123" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K123" s="24" t="str"/>
       <x:c r="L123" s="24"/>
@@ -5319,7 +5320,7 @@
       </x:c>
       <x:c r="I124" s="24" t="str"/>
       <x:c r="J124" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K124" s="24" t="str"/>
       <x:c r="L124" s="24"/>
@@ -5351,7 +5352,7 @@
       </x:c>
       <x:c r="I125" s="24" t="str"/>
       <x:c r="J125" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K125" s="24" t="str"/>
       <x:c r="L125" s="24"/>
@@ -5383,7 +5384,7 @@
       </x:c>
       <x:c r="I126" s="24" t="str"/>
       <x:c r="J126" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K126" s="24" t="str"/>
       <x:c r="L126" s="24"/>
@@ -5415,7 +5416,7 @@
       </x:c>
       <x:c r="I127" s="24" t="str"/>
       <x:c r="J127" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K127" s="24" t="str"/>
       <x:c r="L127" s="24"/>
@@ -5447,7 +5448,7 @@
       </x:c>
       <x:c r="I128" s="24" t="str"/>
       <x:c r="J128" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K128" s="24" t="str"/>
       <x:c r="L128" s="24"/>
@@ -5479,7 +5480,7 @@
       </x:c>
       <x:c r="I129" s="24" t="str"/>
       <x:c r="J129" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K129" s="24" t="str"/>
       <x:c r="L129" s="24"/>
@@ -5511,7 +5512,7 @@
       </x:c>
       <x:c r="I130" s="24" t="str"/>
       <x:c r="J130" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K130" s="24" t="str"/>
       <x:c r="L130" s="24"/>
@@ -5543,7 +5544,7 @@
       </x:c>
       <x:c r="I131" s="24" t="str"/>
       <x:c r="J131" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K131" s="24" t="str"/>
       <x:c r="L131" s="24"/>
@@ -5575,7 +5576,7 @@
       </x:c>
       <x:c r="I132" s="24" t="str"/>
       <x:c r="J132" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K132" s="24" t="str"/>
       <x:c r="L132" s="24"/>

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rda264549d40d44ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R5db31af403954d1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="Rcbea06f832c34923"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R0a5b932c22ee4d1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R002746b1e24c4a04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rf3e47b3c97254e16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R834ea45e749c40a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R8226eb8e53f94dfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R1b1ccd7c54434106"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R0352800ba923400b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.5040650406504065</x:v>
+        <x:v>0.5487804878048781</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -909,13 +909,14 @@
         <x:v>Replace direct vendor assignment with a realistic propose-review-accept staffing flow.</x:v>
       </x:c>
       <x:c r="H21" s="25" t="n">
-        <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A21,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A21),0)</x:f>
-        <x:v>0.09090909090909091</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I21" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="J21" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="J21" s="24" t="str">
+        <x:v>Completed 2026-09-07: Vendor candidate submissions, PM-only decisions/acceptance, audited lifecycle, direct-placement retirement, and regression migration.</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A22" s="24" t="str">
@@ -941,7 +942,7 @@
       </x:c>
       <x:c r="H22" s="25" t="n">
         <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A22,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A22),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.125</x:v>
       </x:c>
       <x:c r="I22" s="24" t="str">
         <x:v>☐</x:v>
@@ -1356,14 +1357,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>124</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>121</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1372,7 +1373,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.5061224489795918</x:v>
+        <x:v>0.5510204081632653</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -5608,7 +5609,7 @@
       </x:c>
       <x:c r="I133" s="24" t="str"/>
       <x:c r="J133" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K133" s="24" t="str"/>
       <x:c r="L133" s="24"/>
@@ -5640,7 +5641,7 @@
       </x:c>
       <x:c r="I134" s="24" t="str"/>
       <x:c r="J134" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K134" s="24" t="str"/>
       <x:c r="L134" s="24"/>
@@ -5672,7 +5673,7 @@
       </x:c>
       <x:c r="I135" s="24" t="str"/>
       <x:c r="J135" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K135" s="24" t="str"/>
       <x:c r="L135" s="24"/>
@@ -5704,7 +5705,7 @@
       </x:c>
       <x:c r="I136" s="24" t="str"/>
       <x:c r="J136" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K136" s="24" t="str"/>
       <x:c r="L136" s="24"/>
@@ -5736,7 +5737,7 @@
       </x:c>
       <x:c r="I137" s="24" t="str"/>
       <x:c r="J137" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K137" s="24" t="str"/>
       <x:c r="L137" s="24"/>
@@ -5768,7 +5769,7 @@
       </x:c>
       <x:c r="I138" s="24" t="str"/>
       <x:c r="J138" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K138" s="24" t="str"/>
       <x:c r="L138" s="24"/>
@@ -5800,7 +5801,7 @@
       </x:c>
       <x:c r="I139" s="24" t="str"/>
       <x:c r="J139" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K139" s="24" t="str"/>
       <x:c r="L139" s="24"/>
@@ -5832,7 +5833,7 @@
       </x:c>
       <x:c r="I140" s="24" t="str"/>
       <x:c r="J140" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K140" s="24" t="str"/>
       <x:c r="L140" s="24"/>
@@ -5864,7 +5865,7 @@
       </x:c>
       <x:c r="I141" s="24" t="str"/>
       <x:c r="J141" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K141" s="24" t="str"/>
       <x:c r="L141" s="24"/>
@@ -5896,7 +5897,7 @@
       </x:c>
       <x:c r="I142" s="24" t="str"/>
       <x:c r="J142" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K142" s="24" t="str"/>
       <x:c r="L142" s="24"/>
@@ -5928,7 +5929,7 @@
       </x:c>
       <x:c r="I143" s="24" t="str"/>
       <x:c r="J143" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K143" s="24" t="str"/>
       <x:c r="L143" s="24"/>

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rf3e47b3c97254e16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R834ea45e749c40a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R8226eb8e53f94dfa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R1b1ccd7c54434106"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R0352800ba923400b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rd143ea3bae004c5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R7712d47889d546bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R3f4d853a4df341db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R97a6e8c8dfa746af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R1042c85dbe2f4f0f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.5487804878048781</x:v>
+        <x:v>0.5772357723577236</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -941,13 +941,14 @@
         <x:v>Turn candidate records into operational staffing visibility and highlight items waiting too long.</x:v>
       </x:c>
       <x:c r="H22" s="25" t="n">
-        <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A22,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A22),0)</x:f>
-        <x:v>0.125</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I22" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="J22" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="J22" s="24" t="str">
+        <x:v>Completed 2026-09-07: project response SLA policy, derived candidate funnel and breach visibility, scoped PM/Vendor dashboards, filters, UI, and regression coverage.</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A23" s="24" t="str">
@@ -1357,14 +1358,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>135</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>110</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1373,7 +1374,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.5510204081632653</x:v>
+        <x:v>0.5795918367346938</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -5961,7 +5962,7 @@
       </x:c>
       <x:c r="I144" s="24" t="str"/>
       <x:c r="J144" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K144" s="24" t="str"/>
       <x:c r="L144" s="24"/>
@@ -5993,7 +5994,7 @@
       </x:c>
       <x:c r="I145" s="24" t="str"/>
       <x:c r="J145" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K145" s="24" t="str"/>
       <x:c r="L145" s="24"/>
@@ -6025,7 +6026,7 @@
       </x:c>
       <x:c r="I146" s="24" t="str"/>
       <x:c r="J146" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K146" s="24" t="str"/>
       <x:c r="L146" s="24"/>
@@ -6057,7 +6058,7 @@
       </x:c>
       <x:c r="I147" s="24" t="str"/>
       <x:c r="J147" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K147" s="24" t="str"/>
       <x:c r="L147" s="24"/>
@@ -6089,7 +6090,7 @@
       </x:c>
       <x:c r="I148" s="24" t="str"/>
       <x:c r="J148" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K148" s="24" t="str"/>
       <x:c r="L148" s="24"/>
@@ -6121,7 +6122,7 @@
       </x:c>
       <x:c r="I149" s="24" t="str"/>
       <x:c r="J149" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K149" s="24" t="str"/>
       <x:c r="L149" s="24"/>
@@ -6153,7 +6154,7 @@
       </x:c>
       <x:c r="I150" s="24" t="str"/>
       <x:c r="J150" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K150" s="24" t="str"/>
       <x:c r="L150" s="24"/>

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rd143ea3bae004c5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R7712d47889d546bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R3f4d853a4df341db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R97a6e8c8dfa746af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R1042c85dbe2f4f0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="R57f9052fc6d04011"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Rfa5ef282763e439a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R703e5e49f58b43ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R76651c57dfe7469e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R9b6f1fd2c951405b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.5772357723577236</x:v>
+        <x:v>0.6178861788617886</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -973,13 +973,14 @@
         <x:v>Notify the right role when another role creates work that needs attention.</x:v>
       </x:c>
       <x:c r="H23" s="25" t="n">
-        <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A23,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A23),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="J23" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="J23" s="24" t="str">
+        <x:v>Completed 2026-09-07: post-commit in-app notifications, inbox/preferences UI, expiry materialization, tenant-scoped APIs, and regression verification.</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A24" s="24" t="str">
@@ -1358,14 +1359,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>142</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>103</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1374,7 +1375,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.5795918367346938</x:v>
+        <x:v>0.6204081632653061</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -6186,7 +6187,7 @@
       </x:c>
       <x:c r="I151" s="24" t="str"/>
       <x:c r="J151" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K151" s="24" t="str"/>
       <x:c r="L151" s="24"/>
@@ -6218,7 +6219,7 @@
       </x:c>
       <x:c r="I152" s="24" t="str"/>
       <x:c r="J152" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K152" s="24" t="str"/>
       <x:c r="L152" s="24"/>
@@ -6250,7 +6251,7 @@
       </x:c>
       <x:c r="I153" s="24" t="str"/>
       <x:c r="J153" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K153" s="24" t="str"/>
       <x:c r="L153" s="24"/>
@@ -6282,7 +6283,7 @@
       </x:c>
       <x:c r="I154" s="24" t="str"/>
       <x:c r="J154" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K154" s="24" t="str"/>
       <x:c r="L154" s="24"/>
@@ -6314,7 +6315,7 @@
       </x:c>
       <x:c r="I155" s="24" t="str"/>
       <x:c r="J155" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K155" s="24" t="str"/>
       <x:c r="L155" s="24"/>
@@ -6346,7 +6347,7 @@
       </x:c>
       <x:c r="I156" s="24" t="str"/>
       <x:c r="J156" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K156" s="24" t="str"/>
       <x:c r="L156" s="24"/>
@@ -6378,7 +6379,7 @@
       </x:c>
       <x:c r="I157" s="24" t="str"/>
       <x:c r="J157" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K157" s="24" t="str"/>
       <x:c r="L157" s="24"/>
@@ -6410,7 +6411,7 @@
       </x:c>
       <x:c r="I158" s="24" t="str"/>
       <x:c r="J158" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K158" s="24" t="str"/>
       <x:c r="L158" s="24"/>
@@ -6442,7 +6443,7 @@
       </x:c>
       <x:c r="I159" s="24" t="str"/>
       <x:c r="J159" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K159" s="24" t="str"/>
       <x:c r="L159" s="24"/>
@@ -6474,7 +6475,7 @@
       </x:c>
       <x:c r="I160" s="24" t="str"/>
       <x:c r="J160" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K160" s="24" t="str"/>
       <x:c r="L160" s="24"/>

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="R57f9052fc6d04011"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Rfa5ef282763e439a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R703e5e49f58b43ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R76651c57dfe7469e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R9b6f1fd2c951405b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="R9750dc8e25f64cda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Rdb161345f8d841bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R52223b4a43bb4ce2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R4ba85da9dc9c4690"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="Rc37d568874cf42ba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.6178861788617886</x:v>
+        <x:v>0.6585365853658537</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -1005,13 +1005,14 @@
         <x:v>Separate commercial client bill rates from contractor cost/default rates and make rate changes historically safe.</x:v>
       </x:c>
       <x:c r="H24" s="25" t="n">
-        <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A24,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A24),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I24" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="J24" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="J24" s="24" t="str">
+        <x:v>M15 complete: rate cards, immutable assignment snapshots, and rate history verified.</x:v>
+      </x:c>
     </x:row>
     <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A25" s="24" t="str">
@@ -1359,14 +1360,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>152</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>93</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1375,7 +1376,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.6204081632653061</x:v>
+        <x:v>0.6612244897959184</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -6507,7 +6508,7 @@
       </x:c>
       <x:c r="I161" s="24" t="str"/>
       <x:c r="J161" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K161" s="24" t="str"/>
       <x:c r="L161" s="24"/>
@@ -6539,7 +6540,7 @@
       </x:c>
       <x:c r="I162" s="24" t="str"/>
       <x:c r="J162" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K162" s="24" t="str"/>
       <x:c r="L162" s="24"/>
@@ -6571,7 +6572,7 @@
       </x:c>
       <x:c r="I163" s="24" t="str"/>
       <x:c r="J163" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K163" s="24" t="str"/>
       <x:c r="L163" s="24"/>
@@ -6603,7 +6604,7 @@
       </x:c>
       <x:c r="I164" s="24" t="str"/>
       <x:c r="J164" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K164" s="24" t="str"/>
       <x:c r="L164" s="24"/>
@@ -6635,7 +6636,7 @@
       </x:c>
       <x:c r="I165" s="24" t="str"/>
       <x:c r="J165" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K165" s="24" t="str"/>
       <x:c r="L165" s="24"/>
@@ -6667,7 +6668,7 @@
       </x:c>
       <x:c r="I166" s="24" t="str"/>
       <x:c r="J166" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K166" s="24" t="str"/>
       <x:c r="L166" s="24"/>
@@ -6699,7 +6700,7 @@
       </x:c>
       <x:c r="I167" s="24" t="str"/>
       <x:c r="J167" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K167" s="24" t="str"/>
       <x:c r="L167" s="24"/>
@@ -6731,7 +6732,7 @@
       </x:c>
       <x:c r="I168" s="24" t="str"/>
       <x:c r="J168" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K168" s="24" t="str"/>
       <x:c r="L168" s="24"/>
@@ -6763,7 +6764,7 @@
       </x:c>
       <x:c r="I169" s="24" t="str"/>
       <x:c r="J169" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K169" s="24" t="str"/>
       <x:c r="L169" s="24"/>
@@ -6795,7 +6796,7 @@
       </x:c>
       <x:c r="I170" s="24" t="str"/>
       <x:c r="J170" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K170" s="24" t="str"/>
       <x:c r="L170" s="24"/>

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="R9750dc8e25f64cda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Rdb161345f8d841bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R52223b4a43bb4ce2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R4ba85da9dc9c4690"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="Rc37d568874cf42ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rd71642efd55e435a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R6928aa885e4e4db2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R82172f55fbb6463e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R069a5dacec334e39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R109604f5fe6e43d8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.6585365853658537</x:v>
+        <x:v>0.6991869918699187</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -1037,13 +1037,14 @@
         <x:v>Keep the proven project-wide hours trigger while making milestones understandable and operationally manageable.</x:v>
       </x:c>
       <x:c r="H25" s="25" t="n">
-        <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A25,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A25),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I25" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="J25" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="J25" s="24" t="str">
+        <x:v>M16 complete: milestone metadata, lifecycle safeguards, timeline and verification.</x:v>
+      </x:c>
     </x:row>
     <x:row r="26" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A26" s="24" t="str">
@@ -1069,7 +1070,7 @@
       </x:c>
       <x:c r="H26" s="25" t="n">
         <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A26,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A26),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.14285714285714285</x:v>
       </x:c>
       <x:c r="I26" s="24" t="str">
         <x:v>☐</x:v>
@@ -1360,14 +1361,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>162</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>83</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1376,7 +1377,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.6612244897959184</x:v>
+        <x:v>0.7020408163265306</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -6828,7 +6829,7 @@
       </x:c>
       <x:c r="I171" s="24" t="str"/>
       <x:c r="J171" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K171" s="24" t="str"/>
       <x:c r="L171" s="24"/>
@@ -6860,7 +6861,7 @@
       </x:c>
       <x:c r="I172" s="24" t="str"/>
       <x:c r="J172" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K172" s="24" t="str"/>
       <x:c r="L172" s="24"/>
@@ -6892,7 +6893,7 @@
       </x:c>
       <x:c r="I173" s="24" t="str"/>
       <x:c r="J173" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K173" s="24" t="str"/>
       <x:c r="L173" s="24"/>
@@ -6924,7 +6925,7 @@
       </x:c>
       <x:c r="I174" s="24" t="str"/>
       <x:c r="J174" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K174" s="24" t="str"/>
       <x:c r="L174" s="24"/>
@@ -6956,7 +6957,7 @@
       </x:c>
       <x:c r="I175" s="24" t="str"/>
       <x:c r="J175" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K175" s="24" t="str"/>
       <x:c r="L175" s="24"/>
@@ -6988,7 +6989,7 @@
       </x:c>
       <x:c r="I176" s="24" t="str"/>
       <x:c r="J176" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K176" s="24" t="str"/>
       <x:c r="L176" s="24"/>
@@ -7020,7 +7021,7 @@
       </x:c>
       <x:c r="I177" s="24" t="str"/>
       <x:c r="J177" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K177" s="24" t="str"/>
       <x:c r="L177" s="24"/>
@@ -7052,7 +7053,7 @@
       </x:c>
       <x:c r="I178" s="24" t="str"/>
       <x:c r="J178" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K178" s="24" t="str"/>
       <x:c r="L178" s="24"/>
@@ -7084,7 +7085,7 @@
       </x:c>
       <x:c r="I179" s="24" t="str"/>
       <x:c r="J179" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K179" s="24" t="str"/>
       <x:c r="L179" s="24"/>
@@ -7116,7 +7117,7 @@
       </x:c>
       <x:c r="I180" s="24" t="str"/>
       <x:c r="J180" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K180" s="24" t="str"/>
       <x:c r="L180" s="24"/>

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rd71642efd55e435a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R6928aa885e4e4db2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R82172f55fbb6463e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R069a5dacec334e39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R109604f5fe6e43d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Red77e4215da24836"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R48df308eb2ad4b90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R8178b4a104c14162"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R44b4bb557c3f44e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="Refdd0d417d5441c8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.6991869918699187</x:v>
+        <x:v>0.7398373983739838</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -1069,13 +1069,14 @@
         <x:v>Correct the commercial ownership model: milestones create billing eligibility; Vendor creates/submits an invoice; Client/PM approves or rejects it.</x:v>
       </x:c>
       <x:c r="H26" s="25" t="n">
-        <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A26,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A26),0)</x:f>
-        <x:v>0.14285714285714285</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I26" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="J26" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="J26" s="24" t="str">
+        <x:v>M17 complete: Vendor billing queue, invoice drafts, PM review, and immutable item snapshots.</x:v>
+      </x:c>
     </x:row>
     <x:row r="27" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A27" s="24" t="str">
@@ -1361,14 +1362,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>172</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>73</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1377,7 +1378,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.7020408163265306</x:v>
+        <x:v>0.7428571428571429</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -7149,7 +7150,7 @@
       </x:c>
       <x:c r="I181" s="24" t="str"/>
       <x:c r="J181" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K181" s="24" t="str"/>
       <x:c r="L181" s="24"/>
@@ -7181,7 +7182,7 @@
       </x:c>
       <x:c r="I182" s="24" t="str"/>
       <x:c r="J182" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K182" s="24" t="str"/>
       <x:c r="L182" s="24"/>
@@ -7213,7 +7214,7 @@
       </x:c>
       <x:c r="I183" s="24" t="str"/>
       <x:c r="J183" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K183" s="24" t="str"/>
       <x:c r="L183" s="24"/>
@@ -7245,7 +7246,7 @@
       </x:c>
       <x:c r="I184" s="24" t="str"/>
       <x:c r="J184" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K184" s="24" t="str"/>
       <x:c r="L184" s="24"/>
@@ -7277,7 +7278,7 @@
       </x:c>
       <x:c r="I185" s="24" t="str"/>
       <x:c r="J185" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K185" s="24" t="str"/>
       <x:c r="L185" s="24"/>
@@ -7309,7 +7310,7 @@
       </x:c>
       <x:c r="I186" s="24" t="str"/>
       <x:c r="J186" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K186" s="24" t="str"/>
       <x:c r="L186" s="24"/>
@@ -7341,7 +7342,7 @@
       </x:c>
       <x:c r="I187" s="24" t="str"/>
       <x:c r="J187" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K187" s="24" t="str"/>
       <x:c r="L187" s="24"/>
@@ -7373,7 +7374,7 @@
       </x:c>
       <x:c r="I188" s="24" t="str"/>
       <x:c r="J188" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K188" s="24" t="str"/>
       <x:c r="L188" s="24"/>
@@ -7405,7 +7406,7 @@
       </x:c>
       <x:c r="I189" s="24" t="str"/>
       <x:c r="J189" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K189" s="24" t="str"/>
       <x:c r="L189" s="24"/>
@@ -7437,7 +7438,7 @@
       </x:c>
       <x:c r="I190" s="24" t="str"/>
       <x:c r="J190" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K190" s="24" t="str"/>
       <x:c r="L190" s="24"/>

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Red77e4215da24836"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R48df308eb2ad4b90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R8178b4a104c14162"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R44b4bb557c3f44e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="Refdd0d417d5441c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="R7ed5f5cf8aec4fd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Rc691fb98179742de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R6008729000674cdc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R8f560fd096ab46b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R7fa5bcbea5c84b06"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.7398373983739838</x:v>
+        <x:v>0.7804878048780488</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -1102,7 +1102,7 @@
       </x:c>
       <x:c r="H27" s="25" t="n">
         <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A27,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A27),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I27" s="24" t="str">
         <x:v>☐</x:v>
@@ -1362,14 +1362,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>182</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>63</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1378,7 +1378,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.7428571428571429</x:v>
+        <x:v>0.7836734693877551</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -7534,7 +7534,7 @@
       </x:c>
       <x:c r="I193" s="24" t="str"/>
       <x:c r="J193" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K193" s="24" t="str"/>
       <x:c r="L193" s="24"/>
@@ -7566,7 +7566,7 @@
       </x:c>
       <x:c r="I194" s="24" t="str"/>
       <x:c r="J194" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K194" s="24" t="str"/>
       <x:c r="L194" s="24"/>
@@ -7598,7 +7598,7 @@
       </x:c>
       <x:c r="I195" s="24" t="str"/>
       <x:c r="J195" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K195" s="24" t="str"/>
       <x:c r="L195" s="24"/>
@@ -7630,7 +7630,7 @@
       </x:c>
       <x:c r="I196" s="24" t="str"/>
       <x:c r="J196" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K196" s="24" t="str"/>
       <x:c r="L196" s="24"/>
@@ -7662,7 +7662,7 @@
       </x:c>
       <x:c r="I197" s="24" t="str"/>
       <x:c r="J197" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K197" s="24" t="str"/>
       <x:c r="L197" s="24"/>
@@ -7694,7 +7694,7 @@
       </x:c>
       <x:c r="I198" s="24" t="str"/>
       <x:c r="J198" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K198" s="24" t="str"/>
       <x:c r="L198" s="24"/>
@@ -7726,7 +7726,7 @@
       </x:c>
       <x:c r="I199" s="24" t="str"/>
       <x:c r="J199" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K199" s="24" t="str"/>
       <x:c r="L199" s="24"/>
@@ -7758,7 +7758,7 @@
       </x:c>
       <x:c r="I200" s="24" t="str"/>
       <x:c r="J200" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K200" s="24" t="str"/>
       <x:c r="L200" s="24"/>
@@ -7790,7 +7790,7 @@
       </x:c>
       <x:c r="I201" s="24" t="str"/>
       <x:c r="J201" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K201" s="24" t="str"/>
       <x:c r="L201" s="24"/>
@@ -7822,7 +7822,7 @@
       </x:c>
       <x:c r="I202" s="24" t="str"/>
       <x:c r="J202" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K202" s="24" t="str"/>
       <x:c r="L202" s="24"/>

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="R7ed5f5cf8aec4fd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Rc691fb98179742de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R6008729000674cdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R8f560fd096ab46b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R7fa5bcbea5c84b06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Ra8ca03bd1e9645d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R90e674a0e34a4cc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="Rad9b0a35c05b4998"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R3c65daf67d9d4c57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="Rb58090f29fc0499a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.7804878048780488</x:v>
+        <x:v>0.8211382113821138</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -1133,7 +1133,7 @@
       </x:c>
       <x:c r="H28" s="25" t="n">
         <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A28,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A28),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I28" s="24" t="str">
         <x:v>☐</x:v>
@@ -1362,14 +1362,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>192</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>53</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1378,7 +1378,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.7836734693877551</x:v>
+        <x:v>0.8244897959183674</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -7854,7 +7854,7 @@
       </x:c>
       <x:c r="I203" s="24" t="str"/>
       <x:c r="J203" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K203" s="24" t="str"/>
       <x:c r="L203" s="24"/>
@@ -7886,7 +7886,7 @@
       </x:c>
       <x:c r="I204" s="24" t="str"/>
       <x:c r="J204" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K204" s="24" t="str"/>
       <x:c r="L204" s="24"/>
@@ -7918,7 +7918,7 @@
       </x:c>
       <x:c r="I205" s="24" t="str"/>
       <x:c r="J205" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K205" s="24" t="str"/>
       <x:c r="L205" s="24"/>
@@ -7950,7 +7950,7 @@
       </x:c>
       <x:c r="I206" s="24" t="str"/>
       <x:c r="J206" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K206" s="24" t="str"/>
       <x:c r="L206" s="24"/>
@@ -7982,7 +7982,7 @@
       </x:c>
       <x:c r="I207" s="24" t="str"/>
       <x:c r="J207" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K207" s="24" t="str"/>
       <x:c r="L207" s="24"/>
@@ -8014,7 +8014,7 @@
       </x:c>
       <x:c r="I208" s="24" t="str"/>
       <x:c r="J208" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K208" s="24" t="str"/>
       <x:c r="L208" s="24"/>
@@ -8046,7 +8046,7 @@
       </x:c>
       <x:c r="I209" s="24" t="str"/>
       <x:c r="J209" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K209" s="24" t="str"/>
       <x:c r="L209" s="24"/>
@@ -8078,7 +8078,7 @@
       </x:c>
       <x:c r="I210" s="24" t="str"/>
       <x:c r="J210" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K210" s="24" t="str"/>
       <x:c r="L210" s="24"/>
@@ -8110,7 +8110,7 @@
       </x:c>
       <x:c r="I211" s="24" t="str"/>
       <x:c r="J211" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K211" s="24" t="str"/>
       <x:c r="L211" s="24"/>
@@ -8142,7 +8142,7 @@
       </x:c>
       <x:c r="I212" s="24" t="str"/>
       <x:c r="J212" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K212" s="24" t="str"/>
       <x:c r="L212" s="24"/>

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Ra8ca03bd1e9645d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R90e674a0e34a4cc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="Rad9b0a35c05b4998"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R3c65daf67d9d4c57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="Rb58090f29fc0499a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rfad9b399a9c94f88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R17e40dcb905d489a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R772e6065c2b046eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R7f6bcd8481c44450"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="Rc9fb8b57cb6e4a82"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.8211382113821138</x:v>
+        <x:v>0.8658536585365854</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -1163,13 +1163,14 @@
         <x:v>Make dashboards reflect the full workforce/commercial lifecycle with precise terminology and exportable operational data.</x:v>
       </x:c>
       <x:c r="H29" s="25" t="n">
-        <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A29,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A29),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I29" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="J29" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="J29" s="24" t="str">
+        <x:v>Completed 2026-09-08: M20 dashboards, CSV exports, tests, audit and documentation.</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A30" s="24" t="str">
@@ -1362,14 +1363,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>202</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>43</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1378,7 +1379,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.8244897959183674</x:v>
+        <x:v>0.8693877551020408</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -8174,10 +8175,14 @@
       </x:c>
       <x:c r="I213" s="24" t="str"/>
       <x:c r="J213" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K213" s="24" t="str"/>
-      <x:c r="L213" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K213" s="24" t="str">
+        <x:v>Completed 2026-09-08: dashboards, scoped exports, tests, audit and documentation verified.</x:v>
+      </x:c>
+      <x:c r="L213" s="24" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
     </x:row>
     <x:row r="214" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A214" s="24" t="str">
@@ -8206,10 +8211,14 @@
       </x:c>
       <x:c r="I214" s="24" t="str"/>
       <x:c r="J214" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K214" s="24" t="str"/>
-      <x:c r="L214" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K214" s="24" t="str">
+        <x:v>Completed 2026-09-08: dashboards, scoped exports, tests, audit and documentation verified.</x:v>
+      </x:c>
+      <x:c r="L214" s="24" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
     </x:row>
     <x:row r="215" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A215" s="24" t="str">
@@ -8238,10 +8247,14 @@
       </x:c>
       <x:c r="I215" s="24" t="str"/>
       <x:c r="J215" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K215" s="24" t="str"/>
-      <x:c r="L215" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K215" s="24" t="str">
+        <x:v>Completed 2026-09-08: dashboards, scoped exports, tests, audit and documentation verified.</x:v>
+      </x:c>
+      <x:c r="L215" s="24" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
     </x:row>
     <x:row r="216" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A216" s="24" t="str">
@@ -8270,10 +8283,14 @@
       </x:c>
       <x:c r="I216" s="24" t="str"/>
       <x:c r="J216" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K216" s="24" t="str"/>
-      <x:c r="L216" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K216" s="24" t="str">
+        <x:v>Completed 2026-09-08: dashboards, scoped exports, tests, audit and documentation verified.</x:v>
+      </x:c>
+      <x:c r="L216" s="24" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
     </x:row>
     <x:row r="217" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A217" s="24" t="str">
@@ -8302,10 +8319,14 @@
       </x:c>
       <x:c r="I217" s="24" t="str"/>
       <x:c r="J217" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K217" s="24" t="str"/>
-      <x:c r="L217" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K217" s="24" t="str">
+        <x:v>Completed 2026-09-08: dashboards, scoped exports, tests, audit and documentation verified.</x:v>
+      </x:c>
+      <x:c r="L217" s="24" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
     </x:row>
     <x:row r="218" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A218" s="24" t="str">
@@ -8334,10 +8355,14 @@
       </x:c>
       <x:c r="I218" s="24" t="str"/>
       <x:c r="J218" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K218" s="24" t="str"/>
-      <x:c r="L218" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K218" s="24" t="str">
+        <x:v>Completed 2026-09-08: dashboards, scoped exports, tests, audit and documentation verified.</x:v>
+      </x:c>
+      <x:c r="L218" s="24" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
     </x:row>
     <x:row r="219" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A219" s="24" t="str">
@@ -8366,10 +8391,14 @@
       </x:c>
       <x:c r="I219" s="24" t="str"/>
       <x:c r="J219" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K219" s="24" t="str"/>
-      <x:c r="L219" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K219" s="24" t="str">
+        <x:v>Completed 2026-09-08: dashboards, scoped exports, tests, audit and documentation verified.</x:v>
+      </x:c>
+      <x:c r="L219" s="24" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
     </x:row>
     <x:row r="220" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A220" s="24" t="str">
@@ -8398,10 +8427,14 @@
       </x:c>
       <x:c r="I220" s="24" t="str"/>
       <x:c r="J220" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K220" s="24" t="str"/>
-      <x:c r="L220" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K220" s="24" t="str">
+        <x:v>Completed 2026-09-08: dashboards, scoped exports, tests, audit and documentation verified.</x:v>
+      </x:c>
+      <x:c r="L220" s="24" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
     </x:row>
     <x:row r="221" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A221" s="24" t="str">
@@ -8430,10 +8463,14 @@
       </x:c>
       <x:c r="I221" s="24" t="str"/>
       <x:c r="J221" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K221" s="24" t="str"/>
-      <x:c r="L221" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K221" s="24" t="str">
+        <x:v>Completed 2026-09-08: dashboards, scoped exports, tests, audit and documentation verified.</x:v>
+      </x:c>
+      <x:c r="L221" s="24" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
     </x:row>
     <x:row r="222" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A222" s="24" t="str">
@@ -8462,10 +8499,14 @@
       </x:c>
       <x:c r="I222" s="24" t="str"/>
       <x:c r="J222" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K222" s="24" t="str"/>
-      <x:c r="L222" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K222" s="24" t="str">
+        <x:v>Completed 2026-09-08: dashboards, scoped exports, tests, audit and documentation verified.</x:v>
+      </x:c>
+      <x:c r="L222" s="24" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
     </x:row>
     <x:row r="223" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A223" s="24" t="str">
@@ -8494,10 +8535,14 @@
       </x:c>
       <x:c r="I223" s="24" t="str"/>
       <x:c r="J223" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K223" s="24" t="str"/>
-      <x:c r="L223" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K223" s="24" t="str">
+        <x:v>Completed 2026-09-08: dashboards, scoped exports, tests, audit and documentation verified.</x:v>
+      </x:c>
+      <x:c r="L223" s="24" t="str">
+        <x:v>2026-09-08</x:v>
+      </x:c>
     </x:row>
     <x:row r="224" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A224" s="24" t="str">

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rfad9b399a9c94f88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R17e40dcb905d489a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R772e6065c2b046eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R7f6bcd8481c44450"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="Rc9fb8b57cb6e4a82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="R6d4dcf431023435e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R02202555c45841dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R9506427bb4f24cfc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R37be12a982f34320"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R2f08e573395d4843"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.8658536585365854</x:v>
+        <x:v>0.8983739837398373</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -1196,7 +1196,7 @@
       </x:c>
       <x:c r="H30" s="25" t="n">
         <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A30,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A30),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I30" s="24" t="str">
         <x:v>☐</x:v>
@@ -1363,14 +1363,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>213</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1379,7 +1379,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.8693877551020408</x:v>
+        <x:v>0.9020408163265307</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -8571,9 +8571,9 @@
       </x:c>
       <x:c r="I224" s="24" t="str"/>
       <x:c r="J224" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K224" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K224" s="24"/>
       <x:c r="L224" s="24"/>
     </x:row>
     <x:row r="225" ht="39.599998474121094" hidden="0" customHeight="1">
@@ -8603,9 +8603,9 @@
       </x:c>
       <x:c r="I225" s="24" t="str"/>
       <x:c r="J225" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K225" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K225" s="24"/>
       <x:c r="L225" s="24"/>
     </x:row>
     <x:row r="226" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -8635,9 +8635,9 @@
       </x:c>
       <x:c r="I226" s="24" t="str"/>
       <x:c r="J226" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K226" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K226" s="24"/>
       <x:c r="L226" s="24"/>
     </x:row>
     <x:row r="227" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -8667,9 +8667,9 @@
       </x:c>
       <x:c r="I227" s="24" t="str"/>
       <x:c r="J227" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K227" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K227" s="24"/>
       <x:c r="L227" s="24"/>
     </x:row>
     <x:row r="228" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -8699,9 +8699,9 @@
       </x:c>
       <x:c r="I228" s="24" t="str"/>
       <x:c r="J228" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K228" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K228" s="24"/>
       <x:c r="L228" s="24"/>
     </x:row>
     <x:row r="229" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -8731,9 +8731,9 @@
       </x:c>
       <x:c r="I229" s="24" t="str"/>
       <x:c r="J229" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K229" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K229" s="24"/>
       <x:c r="L229" s="24"/>
     </x:row>
     <x:row r="230" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -8763,9 +8763,9 @@
       </x:c>
       <x:c r="I230" s="24" t="str"/>
       <x:c r="J230" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K230" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K230" s="24"/>
       <x:c r="L230" s="24"/>
     </x:row>
     <x:row r="231" ht="26.399999618530273" hidden="0" customHeight="1">
@@ -8795,9 +8795,9 @@
       </x:c>
       <x:c r="I231" s="24" t="str"/>
       <x:c r="J231" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K231" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K231" s="24"/>
       <x:c r="L231" s="24"/>
     </x:row>
     <x:row r="232" ht="26.399999618530273" hidden="0" customHeight="1">

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="R6d4dcf431023435e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R02202555c45841dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R9506427bb4f24cfc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R37be12a982f34320"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R2f08e573395d4843"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Ra7d5c122cabd4c0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Rac734a2736024cca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="Re79bfcc9a7984f07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R92be456dbd95407b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="Raa438b85fc4540a9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="14" t="n">
         <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.8983739837398373</x:v>
+        <x:v>0.943089430894309</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -1227,12 +1227,14 @@
       </x:c>
       <x:c r="H31" s="25" t="n">
         <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A31,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A31),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I31" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="J31" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="J31" s="24" t="str">
+        <x:v>Completed 2026-09-09: Docker demo, checksum ledger, deterministic seed, Playwright E2E, backup/restore, security review, performance smoke, and full regression verified.</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A32" s="24" t="str">
@@ -1363,14 +1365,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>221</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1379,7 +1381,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.9020408163265307</x:v>
+        <x:v>0.9469387755102041</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -8827,7 +8829,7 @@
       </x:c>
       <x:c r="I232" s="24" t="str"/>
       <x:c r="J232" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K232" s="24" t="str"/>
       <x:c r="L232" s="24"/>
@@ -8859,7 +8861,7 @@
       </x:c>
       <x:c r="I233" s="24" t="str"/>
       <x:c r="J233" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K233" s="24" t="str"/>
       <x:c r="L233" s="24"/>
@@ -8891,7 +8893,7 @@
       </x:c>
       <x:c r="I234" s="24" t="str"/>
       <x:c r="J234" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K234" s="24" t="str"/>
       <x:c r="L234" s="24"/>
@@ -8923,7 +8925,7 @@
       </x:c>
       <x:c r="I235" s="24" t="str"/>
       <x:c r="J235" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K235" s="24" t="str"/>
       <x:c r="L235" s="24"/>
@@ -8955,7 +8957,7 @@
       </x:c>
       <x:c r="I236" s="24" t="str"/>
       <x:c r="J236" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K236" s="24" t="str"/>
       <x:c r="L236" s="24"/>
@@ -8987,7 +8989,7 @@
       </x:c>
       <x:c r="I237" s="24" t="str"/>
       <x:c r="J237" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K237" s="24" t="str"/>
       <x:c r="L237" s="24"/>
@@ -9019,7 +9021,7 @@
       </x:c>
       <x:c r="I238" s="24" t="str"/>
       <x:c r="J238" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K238" s="24" t="str"/>
       <x:c r="L238" s="24"/>
@@ -9051,7 +9053,7 @@
       </x:c>
       <x:c r="I239" s="24" t="str"/>
       <x:c r="J239" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K239" s="24" t="str"/>
       <x:c r="L239" s="24"/>
@@ -9083,7 +9085,7 @@
       </x:c>
       <x:c r="I240" s="24" t="str"/>
       <x:c r="J240" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K240" s="24" t="str"/>
       <x:c r="L240" s="24"/>
@@ -9115,7 +9117,7 @@
       </x:c>
       <x:c r="I241" s="24" t="str"/>
       <x:c r="J241" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K241" s="24" t="str"/>
       <x:c r="L241" s="24"/>
@@ -9147,7 +9149,7 @@
       </x:c>
       <x:c r="I242" s="24" t="str"/>
       <x:c r="J242" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K242" s="24" t="str"/>
       <x:c r="L242" s="24"/>

--- a/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
+++ b/Expansion/Workday_VMS_Expansion_Feature_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Ra7d5c122cabd4c0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="Rac734a2736024cca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="Re79bfcc9a7984f07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R92be456dbd95407b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="Raa438b85fc4540a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap" sheetId="1" r:id="Rdcc95915d4fd4b5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="2" r:id="R6b1498aad2184f83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependencies" sheetId="3" r:id="R5da5e29a798a497b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="4" r:id="R857188139bf84c21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R20541007203f476e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -465,8 +465,8 @@
         <x:v>Overall completion</x:v>
       </x:c>
       <x:c r="B6" s="14" t="n">
-        <x:f>IFERROR(COUNTIF(Checklist!$J$2:$J$400,"☑")/COUNTA(Checklist!$G$2:$G$400),0)</x:f>
-        <x:v>0.943089430894309</x:v>
+        <x:f>IFERROR(COUNTIF(Checklist!$J$8:$J$400,"☑")/COUNTA(Checklist!$G$8:$G$400),0)</x:f>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -850,7 +850,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="J19" s="24" t="str"/>
     </x:row>
@@ -1105,7 +1105,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I27" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="J27" s="24" t="str"/>
     </x:row>
@@ -1136,7 +1136,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I28" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="J28" s="24" t="str"/>
     </x:row>
@@ -1199,7 +1199,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I30" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="J30" s="24" t="str"/>
     </x:row>
@@ -1259,13 +1259,14 @@
         <x:v>Validate that the expanded platform is coherent, tested and explainable, then cut a portfolio release.</x:v>
       </x:c>
       <x:c r="H32" s="25" t="n">
-        <x:f>IFERROR(COUNTIFS(Checklist!$A$2:$A$400,A32,Checklist!$J$2:$J$400,"☑")/COUNTIF(Checklist!$A$2:$A$400,A32),0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I32" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="J32" s="24" t="str"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="J32" s="24" t="str">
+        <x:v>Completed 2026-09-09: final architecture/security/authorization audit, financial reconciliation, release documentation, interview story, and tracker reconciliation verified.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1365,14 +1366,14 @@
       </x:c>
       <x:c r="B4" t="n">
         <x:f>COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>232</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C4" t="str">
         <x:v>Remaining</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:f>COUNTA(G8:G400)-COUNTIF(J8:J400,"☑")</x:f>
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1381,7 +1382,7 @@
       </x:c>
       <x:c r="B5" s="14" t="n">
         <x:f>IFERROR(B4/COUNTA(G8:G400),0)</x:f>
-        <x:v>0.9469387755102041</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str"/>
@@ -5233,7 +5234,7 @@
       </x:c>
       <x:c r="I121" s="24" t="str"/>
       <x:c r="J121" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K121" s="24" t="str"/>
       <x:c r="L121" s="24"/>
@@ -7473,7 +7474,7 @@
       </x:c>
       <x:c r="I191" s="24" t="str"/>
       <x:c r="J191" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K191" s="24" t="str"/>
       <x:c r="L191" s="24"/>
@@ -7505,7 +7506,7 @@
       </x:c>
       <x:c r="I192" s="24" t="str"/>
       <x:c r="J192" s="24" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="K192" s="24" t="str"/>
       <x:c r="L192" s="24"/>
@@ -9181,10 +9182,14 @@
       </x:c>
       <x:c r="I243" s="24" t="str"/>
       <x:c r="J243" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K243" s="24" t="str"/>
-      <x:c r="L243" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K243" s="24" t="str">
+        <x:v>Completed in M23 final audit and release-preparation pass.</x:v>
+      </x:c>
+      <x:c r="L243" s="24" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
     </x:row>
     <x:row r="244" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A244" s="24" t="str">
@@ -9213,10 +9218,14 @@
       </x:c>
       <x:c r="I244" s="24" t="str"/>
       <x:c r="J244" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K244" s="24" t="str"/>
-      <x:c r="L244" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K244" s="24" t="str">
+        <x:v>Completed in M23 final audit and release-preparation pass.</x:v>
+      </x:c>
+      <x:c r="L244" s="24" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
     </x:row>
     <x:row r="245" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A245" s="24" t="str">
@@ -9245,10 +9254,14 @@
       </x:c>
       <x:c r="I245" s="24" t="str"/>
       <x:c r="J245" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K245" s="24" t="str"/>
-      <x:c r="L245" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K245" s="24" t="str">
+        <x:v>Completed in M23 final audit and release-preparation pass.</x:v>
+      </x:c>
+      <x:c r="L245" s="24" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
     </x:row>
     <x:row r="246" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A246" s="24" t="str">
@@ -9277,10 +9290,14 @@
       </x:c>
       <x:c r="I246" s="24" t="str"/>
       <x:c r="J246" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K246" s="24" t="str"/>
-      <x:c r="L246" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K246" s="24" t="str">
+        <x:v>Completed in M23 final audit and release-preparation pass.</x:v>
+      </x:c>
+      <x:c r="L246" s="24" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
     </x:row>
     <x:row r="247" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A247" s="24" t="str">
@@ -9309,10 +9326,14 @@
       </x:c>
       <x:c r="I247" s="24" t="str"/>
       <x:c r="J247" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K247" s="24" t="str"/>
-      <x:c r="L247" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K247" s="24" t="str">
+        <x:v>Completed in M23 final audit and release-preparation pass.</x:v>
+      </x:c>
+      <x:c r="L247" s="24" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
     </x:row>
     <x:row r="248" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A248" s="24" t="str">
@@ -9341,10 +9362,14 @@
       </x:c>
       <x:c r="I248" s="24" t="str"/>
       <x:c r="J248" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K248" s="24" t="str"/>
-      <x:c r="L248" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K248" s="24" t="str">
+        <x:v>Completed in M23 final audit and release-preparation pass.</x:v>
+      </x:c>
+      <x:c r="L248" s="24" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
     </x:row>
     <x:row r="249" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A249" s="24" t="str">
@@ -9373,10 +9398,14 @@
       </x:c>
       <x:c r="I249" s="24" t="str"/>
       <x:c r="J249" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K249" s="24" t="str"/>
-      <x:c r="L249" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K249" s="24" t="str">
+        <x:v>Completed in M23 final audit and release-preparation pass.</x:v>
+      </x:c>
+      <x:c r="L249" s="24" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
     </x:row>
     <x:row r="250" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A250" s="24" t="str">
@@ -9405,10 +9434,14 @@
       </x:c>
       <x:c r="I250" s="24" t="str"/>
       <x:c r="J250" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K250" s="24" t="str"/>
-      <x:c r="L250" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K250" s="24" t="str">
+        <x:v>Completed in M23 final audit and release-preparation pass.</x:v>
+      </x:c>
+      <x:c r="L250" s="24" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
     </x:row>
     <x:row r="251" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A251" s="24" t="str">
@@ -9437,10 +9470,14 @@
       </x:c>
       <x:c r="I251" s="24" t="str"/>
       <x:c r="J251" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K251" s="24" t="str"/>
-      <x:c r="L251" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K251" s="24" t="str">
+        <x:v>Completed in M23 final audit and release-preparation pass.</x:v>
+      </x:c>
+      <x:c r="L251" s="24" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
     </x:row>
     <x:row r="252" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A252" s="24" t="str">
@@ -9469,10 +9506,14 @@
       </x:c>
       <x:c r="I252" s="24" t="str"/>
       <x:c r="J252" s="24" t="str">
-        <x:v>☐</x:v>
-      </x:c>
-      <x:c r="K252" s="24" t="str"/>
-      <x:c r="L252" s="24"/>
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="K252" s="24" t="str">
+        <x:v>Completed in M23 final audit and release-preparation pass.</x:v>
+      </x:c>
+      <x:c r="L252" s="24" t="str">
+        <x:v>2026-09-09</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
